--- a/output/pdf_financials_xlsx/AZT.xlsx
+++ b/output/pdf_financials_xlsx/AZT.xlsx
@@ -858,28 +858,28 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.018711</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.017976</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.003189</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001889</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.017703</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.011907</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.020244</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.045291</v>
       </c>
     </row>
     <row r="13">
@@ -1516,28 +1516,28 @@
         <v>-0.317139</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.46794</v>
+        <v>-1.486651</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.019383</v>
+        <v>-1.037359</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.556881</v>
+        <v>-0.56007</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.423843</v>
+        <v>-1.425732</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.697706</v>
+        <v>-1.715409</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.812552</v>
+        <v>-1.824459</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.824515</v>
+        <v>-1.844759</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.868172</v>
+        <v>-1.913463</v>
       </c>
     </row>
     <row r="28">
@@ -1596,28 +1596,28 @@
         <v>-0.317139</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.46794</v>
+        <v>-1.486651</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.019383</v>
+        <v>-1.037359</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.556881</v>
+        <v>-0.56007</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.423843</v>
+        <v>-1.425732</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.697706</v>
+        <v>-1.715409</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.812552</v>
+        <v>-1.824459</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.824515</v>
+        <v>-1.844759</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.868172</v>
+        <v>-1.913463</v>
       </c>
     </row>
     <row r="30">
@@ -1806,31 +1806,31 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.582142</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.57166</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.645508</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.049755</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.919485</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.471056</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.48559</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.109496</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>8.844626999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1890,31 +1890,31 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.582142</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.57166</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.645508</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.049755</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.919485</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.471056</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.48559</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.109496</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>8.844626999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2394,31 +2394,31 @@
         <v>1e-06</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.584592</v>
+        <v>0.00245</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.648843</v>
+        <v>0.077183</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.7786729999999999</v>
+        <v>0.133165</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.164969</v>
+        <v>0.115214</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.038377</v>
+        <v>0.118892</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.601617</v>
+        <v>0.130561</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.724782</v>
+        <v>0.239192</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.256557</v>
+        <v>0.147061</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>9.018622000000001</v>
+        <v>0.173995</v>
       </c>
     </row>
     <row r="49">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
